--- a/SuppXLS/Scen_Par-SYS_CB_Overshoot_300MT.xlsx
+++ b/SuppXLS/Scen_Par-SYS_CB_Overshoot_300MT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model-VAv2\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\Integrated saturation V1.1\Integrated v1.0\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8DD080-FFE2-4CC6-AF81-2B40AB80DFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09664C97-DBB5-48CB-B505-F82AEBD8FE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="24" r:id="rId1"/>
@@ -764,7 +764,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -848,7 +848,6 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5347,13 +5346,13 @@
       <c r="C9" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="42" t="s">
+      <c r="F9" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5737,7 +5736,7 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="2" max="2" width="34.6328125" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.453125" bestFit="1" customWidth="1"/>
